--- a/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
@@ -602,7 +602,7 @@
         <v>360</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>1.5</v>
@@ -612,7 +612,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Enemy_Dummy</t>
+          <t>Enemy</t>
         </is>
       </c>
     </row>

--- a/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,11 @@
           <t>prefab</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pathRefreshInterval</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,6 +535,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -580,6 +590,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>预制体</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>路径刷新间隔</t>
         </is>
       </c>
     </row>
@@ -615,6 +630,9 @@
           <t>Enemy</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -648,12 +666,10 @@
           <t>Enemy_Assault</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>0.3</v>
+      </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -483,6 +483,11 @@
           <t>pathRefreshInterval</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>chaseRange</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -540,6 +545,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -595,6 +605,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>路径刷新间隔</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>仇恨范围（追击触发距离）</t>
         </is>
       </c>
     </row>
@@ -633,6 +648,9 @@
       <c r="K4" t="n">
         <v>0.3</v>
       </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -668,6 +686,9 @@
       </c>
       <c r="K5" t="n">
         <v>0.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
